--- a/public/workReportDefaultTemplate.xlsx
+++ b/public/workReportDefaultTemplate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\furugakihiromitsu\source\repos\WorkTimeManagementV2\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DACA7C8-D305-4836-A10A-5D4B1DAE491F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B95D6CF-63C2-4448-9CBC-42EDA699692D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,20 @@
     <definedName name="備考">作業報告書!$A$47</definedName>
     <definedName name="曜日">作業報告書!$C$14:$C$44</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -155,13 +168,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
-    <numFmt numFmtId="177" formatCode="&quot;【&quot;yyyy&quot;年&quot;m&quot;月&quot;&quot;度&quot;&quot;勤&quot;&quot;務&quot;&quot;表&quot;&quot;】&quot;"/>
-    <numFmt numFmtId="178" formatCode="[h]:mm"/>
-    <numFmt numFmtId="179" formatCode="0.00_ "/>
-    <numFmt numFmtId="180" formatCode="h:mm;@"/>
-    <numFmt numFmtId="181" formatCode="0.0&quot;日&quot;"/>
+    <numFmt numFmtId="176" formatCode="&quot;【&quot;yyyy&quot;年&quot;m&quot;月&quot;&quot;度&quot;&quot;勤&quot;&quot;務&quot;&quot;表&quot;&quot;】&quot;"/>
+    <numFmt numFmtId="177" formatCode="[h]:mm"/>
+    <numFmt numFmtId="178" formatCode="0.00_ "/>
+    <numFmt numFmtId="179" formatCode="h:mm;@"/>
+    <numFmt numFmtId="180" formatCode="0.0&quot;日&quot;"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -237,22 +250,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Meiryo UI"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF328278"/>
-      <name val="Meiryo UI"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <b/>
       <sz val="18"/>
       <name val="Meiryo UI"/>
       <family val="3"/>
@@ -736,17 +733,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -755,7 +749,7 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -764,12 +758,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -777,18 +765,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -810,13 +786,6 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
@@ -857,22 +826,22 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -881,19 +850,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -921,11 +890,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
       <protection locked="0"/>
     </xf>
@@ -938,7 +907,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -956,10 +925,10 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="4" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="4" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -977,70 +946,50 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="177" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
       <protection locked="0"/>
     </xf>
@@ -1110,10 +1059,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1122,20 +1071,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1202,9 +1154,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1242,7 +1194,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1348,7 +1300,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1490,7 +1442,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1503,1654 +1455,1504 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC49"/>
-  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" outlineLevelRow="1" outlineLevelCol="1"/>
+  <dimension ref="A1:V49"/>
+  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="24" width="5.125" style="4" customWidth="1"/>
-    <col min="25" max="25" width="5.125" style="4" customWidth="1" collapsed="1"/>
-    <col min="26" max="27" width="8.625" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="28" max="28" width="5.125" style="14" customWidth="1"/>
-    <col min="29" max="29" width="91.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="12.625" style="4"/>
+    <col min="1" max="22" width="5.125" style="3" customWidth="1"/>
+    <col min="23" max="16384" width="12.625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="23.1" customHeight="1">
-      <c r="A1" s="48"/>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
+    <row r="1" spans="1:22" ht="23.1" customHeight="1">
+      <c r="A1" s="39"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
       <c r="K1" s="1"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
-      <c r="Q1" s="51" t="s">
+      <c r="Q1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="R1" s="52"/>
-      <c r="S1" s="75"/>
-      <c r="T1" s="75"/>
-      <c r="U1" s="75"/>
-      <c r="V1" s="75"/>
-      <c r="W1" s="24"/>
-      <c r="X1" s="24"/>
-      <c r="Y1" s="24"/>
-      <c r="Z1" s="3"/>
-      <c r="AA1" s="2"/>
-    </row>
-    <row r="2" spans="1:29" ht="23.1" customHeight="1" thickBot="1">
-      <c r="A2" s="50"/>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="53"/>
-      <c r="R2" s="53"/>
-      <c r="S2" s="76"/>
-      <c r="T2" s="76"/>
-      <c r="U2" s="76"/>
-      <c r="V2" s="76"/>
-      <c r="W2" s="24"/>
-      <c r="X2" s="24"/>
-      <c r="Y2" s="24"/>
-      <c r="Z2" s="3"/>
-      <c r="AA2" s="2"/>
-    </row>
-    <row r="3" spans="1:29" ht="23.1" customHeight="1">
-      <c r="A3" s="7"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="19"/>
-      <c r="J3" s="19"/>
-      <c r="K3" s="19"/>
-      <c r="L3" s="19"/>
-      <c r="M3" s="19"/>
-      <c r="N3" s="8"/>
-      <c r="O3" s="8"/>
-      <c r="P3" s="8"/>
-      <c r="Q3" s="8"/>
-      <c r="R3" s="8"/>
-      <c r="S3" s="8"/>
-      <c r="T3" s="8"/>
-      <c r="U3" s="8"/>
-      <c r="V3" s="8"/>
-      <c r="W3" s="8"/>
-      <c r="X3" s="8"/>
-      <c r="Y3" s="8"/>
-      <c r="Z3" s="8"/>
-      <c r="AA3" s="9"/>
-      <c r="AC3" s="17"/>
-    </row>
-    <row r="4" spans="1:29" ht="23.1" customHeight="1" outlineLevel="1">
-      <c r="A4" s="54" t="s">
+      <c r="R1" s="43"/>
+      <c r="S1" s="66"/>
+      <c r="T1" s="66"/>
+      <c r="U1" s="66"/>
+      <c r="V1" s="66"/>
+    </row>
+    <row r="2" spans="1:22" ht="23.1" customHeight="1" thickBot="1">
+      <c r="A2" s="41"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="44"/>
+      <c r="R2" s="44"/>
+      <c r="S2" s="67"/>
+      <c r="T2" s="67"/>
+      <c r="U2" s="67"/>
+      <c r="V2" s="67"/>
+    </row>
+    <row r="3" spans="1:22" ht="23.1" customHeight="1">
+      <c r="A3" s="6"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7"/>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="7"/>
+      <c r="S3" s="7"/>
+      <c r="T3" s="7"/>
+      <c r="U3" s="7"/>
+      <c r="V3" s="7"/>
+    </row>
+    <row r="4" spans="1:22" ht="23.1" customHeight="1" outlineLevel="1">
+      <c r="A4" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="55"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="57">
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="48">
         <v>0.375</v>
       </c>
-      <c r="F4" s="57"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="59" t="s">
+      <c r="F4" s="48"/>
+      <c r="G4" s="49"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="60"/>
-      <c r="K4" s="61"/>
-      <c r="L4" s="68">
+      <c r="J4" s="51"/>
+      <c r="K4" s="52"/>
+      <c r="L4" s="59">
         <f>COUNT(稼働時間, "&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="M4" s="69"/>
-      <c r="O4" s="70" t="s">
+      <c r="M4" s="60"/>
+      <c r="O4" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="P4" s="71"/>
-      <c r="Q4" s="72"/>
-      <c r="R4" s="62">
+      <c r="P4" s="62"/>
+      <c r="Q4" s="63"/>
+      <c r="R4" s="53">
         <f>SUM(稼働時間)</f>
         <v>0</v>
       </c>
-      <c r="S4" s="63"/>
-      <c r="T4" s="64"/>
-      <c r="U4" s="8"/>
-      <c r="V4" s="27"/>
-      <c r="W4" s="13"/>
-      <c r="X4" s="77"/>
-      <c r="Y4" s="78"/>
-      <c r="AB4" s="15"/>
-      <c r="AC4" s="16"/>
-    </row>
-    <row r="5" spans="1:29" ht="23.1" customHeight="1" outlineLevel="1">
-      <c r="A5" s="54" t="s">
+      <c r="S4" s="54"/>
+      <c r="T4" s="55"/>
+      <c r="U4" s="7"/>
+      <c r="V4" s="18"/>
+    </row>
+    <row r="5" spans="1:22" ht="23.1" customHeight="1" outlineLevel="1">
+      <c r="A5" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="55"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="56"/>
-      <c r="E5" s="57">
+      <c r="B5" s="46"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="48">
         <v>0.75</v>
       </c>
-      <c r="F5" s="57"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="20"/>
-      <c r="O5" s="73"/>
-      <c r="P5" s="59"/>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="65"/>
-      <c r="S5" s="66"/>
-      <c r="T5" s="67"/>
-      <c r="U5" s="8"/>
-      <c r="V5" s="26"/>
-      <c r="W5" s="23"/>
-      <c r="X5" s="79"/>
-      <c r="Y5" s="80"/>
-      <c r="AB5" s="15"/>
-      <c r="AC5" s="16"/>
-    </row>
-    <row r="6" spans="1:29" ht="23.1" customHeight="1" outlineLevel="1">
-      <c r="A6" s="54" t="s">
+      <c r="F5" s="48"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="13"/>
+      <c r="O5" s="64"/>
+      <c r="P5" s="50"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="56"/>
+      <c r="S5" s="57"/>
+      <c r="T5" s="58"/>
+      <c r="U5" s="7"/>
+      <c r="V5" s="17"/>
+    </row>
+    <row r="6" spans="1:22" ht="23.1" customHeight="1" outlineLevel="1">
+      <c r="A6" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="55"/>
-      <c r="C6" s="55"/>
-      <c r="D6" s="56"/>
-      <c r="E6" s="83">
+      <c r="B6" s="46"/>
+      <c r="C6" s="46"/>
+      <c r="D6" s="47"/>
+      <c r="E6" s="68">
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="F6" s="57"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="81"/>
-      <c r="J6" s="81"/>
-      <c r="K6" s="81"/>
-      <c r="L6" s="82"/>
-      <c r="M6" s="82"/>
-      <c r="O6" s="13"/>
-      <c r="Q6" s="13"/>
-      <c r="R6" s="22"/>
-      <c r="S6" s="21"/>
-      <c r="T6" s="21"/>
-      <c r="U6" s="8"/>
-      <c r="V6" s="23"/>
-      <c r="W6" s="23"/>
-      <c r="X6" s="80"/>
-      <c r="Y6" s="80"/>
-      <c r="AB6" s="15"/>
-      <c r="AC6" s="16"/>
-    </row>
-    <row r="7" spans="1:29" ht="23.1" customHeight="1" outlineLevel="1">
-      <c r="A7" s="54" t="s">
+      <c r="F6" s="48"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="109"/>
+      <c r="M6" s="109"/>
+      <c r="O6" s="10"/>
+      <c r="Q6" s="10"/>
+      <c r="R6" s="15"/>
+      <c r="S6" s="14"/>
+      <c r="T6" s="14"/>
+      <c r="U6" s="7"/>
+      <c r="V6" s="16"/>
+    </row>
+    <row r="7" spans="1:22" ht="23.1" customHeight="1" outlineLevel="1">
+      <c r="A7" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="55"/>
-      <c r="C7" s="55"/>
-      <c r="D7" s="56"/>
-      <c r="E7" s="121">
+      <c r="B7" s="46"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="47"/>
+      <c r="E7" s="106">
         <f>IF(E5="","",E5-E4-E6)</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="F7" s="122"/>
-      <c r="G7" s="123"/>
-      <c r="H7" s="20"/>
-      <c r="I7" s="81"/>
-      <c r="J7" s="81"/>
-      <c r="K7" s="81"/>
-      <c r="L7" s="82"/>
-      <c r="M7" s="82"/>
-      <c r="O7" s="13"/>
-      <c r="P7" s="13"/>
-      <c r="Q7" s="13"/>
-      <c r="R7" s="21"/>
-      <c r="S7" s="21"/>
-      <c r="T7" s="21"/>
-      <c r="U7" s="8"/>
-      <c r="V7" s="23"/>
-      <c r="W7" s="23"/>
-      <c r="X7" s="80"/>
-      <c r="Y7" s="80"/>
-      <c r="AB7" s="15"/>
-      <c r="AC7" s="16"/>
-    </row>
-    <row r="8" spans="1:29" ht="23.1" customHeight="1" outlineLevel="1">
-      <c r="A8" s="104" t="s">
+      <c r="F7" s="107"/>
+      <c r="G7" s="108"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="109"/>
+      <c r="M7" s="109"/>
+      <c r="O7" s="10"/>
+      <c r="P7" s="10"/>
+      <c r="Q7" s="10"/>
+      <c r="R7" s="14"/>
+      <c r="S7" s="14"/>
+      <c r="T7" s="14"/>
+      <c r="U7" s="7"/>
+      <c r="V7" s="16"/>
+    </row>
+    <row r="8" spans="1:22" ht="23.1" customHeight="1" outlineLevel="1">
+      <c r="A8" s="89" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="55"/>
-      <c r="C8" s="55"/>
-      <c r="D8" s="55"/>
-      <c r="E8" s="105" t="s">
+      <c r="B8" s="46"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="F8" s="106"/>
-      <c r="G8" s="107"/>
-      <c r="H8" s="8"/>
-      <c r="U8" s="8"/>
-      <c r="AB8" s="15"/>
-      <c r="AC8" s="16"/>
-    </row>
-    <row r="9" spans="1:29" ht="23.1" customHeight="1" outlineLevel="1">
-      <c r="A9" s="104" t="s">
+      <c r="F8" s="91"/>
+      <c r="G8" s="92"/>
+      <c r="H8" s="7"/>
+      <c r="U8" s="7"/>
+    </row>
+    <row r="9" spans="1:22" ht="23.1" customHeight="1" outlineLevel="1">
+      <c r="A9" s="89" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="55"/>
-      <c r="C9" s="55"/>
-      <c r="D9" s="55"/>
-      <c r="E9" s="105" t="s">
+      <c r="B9" s="46"/>
+      <c r="C9" s="46"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="F9" s="106"/>
-      <c r="G9" s="107"/>
-      <c r="H9" s="8"/>
-      <c r="O9" s="8"/>
-      <c r="U9" s="8"/>
-      <c r="V9" s="8"/>
-      <c r="W9" s="8"/>
-      <c r="X9" s="8"/>
-      <c r="Y9" s="8"/>
-      <c r="AA9" s="10"/>
-      <c r="AB9" s="15"/>
-      <c r="AC9" s="16"/>
-    </row>
-    <row r="10" spans="1:29" ht="23.1" customHeight="1" outlineLevel="1">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="8"/>
-      <c r="P10" s="8"/>
-      <c r="Q10" s="8"/>
-      <c r="R10" s="8"/>
-      <c r="S10" s="8"/>
-      <c r="T10" s="8"/>
-      <c r="U10" s="8"/>
-      <c r="V10" s="8"/>
-      <c r="W10" s="8"/>
-      <c r="X10" s="8"/>
-      <c r="Y10" s="8"/>
-      <c r="Z10" s="8"/>
-      <c r="AA10" s="9"/>
-      <c r="AB10" s="15"/>
-      <c r="AC10" s="16"/>
-    </row>
-    <row r="11" spans="1:29" ht="23.1" customHeight="1">
-      <c r="A11" s="94" t="s">
+      <c r="F9" s="91"/>
+      <c r="G9" s="92"/>
+      <c r="H9" s="7"/>
+      <c r="O9" s="7"/>
+      <c r="U9" s="7"/>
+      <c r="V9" s="7"/>
+    </row>
+    <row r="10" spans="1:22" ht="23.1" customHeight="1" outlineLevel="1">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+      <c r="O10" s="7"/>
+      <c r="P10" s="7"/>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="7"/>
+      <c r="S10" s="7"/>
+      <c r="T10" s="7"/>
+      <c r="U10" s="7"/>
+      <c r="V10" s="7"/>
+    </row>
+    <row r="11" spans="1:22" ht="23.1" customHeight="1">
+      <c r="A11" s="79" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="108"/>
-      <c r="C11" s="109"/>
-      <c r="D11" s="94" t="s">
+      <c r="B11" s="93"/>
+      <c r="C11" s="94"/>
+      <c r="D11" s="79" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="95"/>
-      <c r="F11" s="94" t="s">
+      <c r="E11" s="80"/>
+      <c r="F11" s="79" t="s">
         <v>14</v>
       </c>
-      <c r="G11" s="95"/>
-      <c r="H11" s="94" t="s">
+      <c r="G11" s="80"/>
+      <c r="H11" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="I11" s="95"/>
-      <c r="J11" s="98" t="s">
+      <c r="I11" s="80"/>
+      <c r="J11" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="K11" s="99"/>
-      <c r="L11" s="98" t="s">
+      <c r="K11" s="84"/>
+      <c r="L11" s="83" t="s">
         <v>15</v>
       </c>
-      <c r="M11" s="102"/>
-      <c r="N11" s="102"/>
-      <c r="O11" s="102"/>
-      <c r="P11" s="102"/>
-      <c r="Q11" s="102"/>
-      <c r="R11" s="102"/>
-      <c r="S11" s="102"/>
-      <c r="T11" s="102"/>
-      <c r="U11" s="102"/>
-      <c r="V11" s="99"/>
-      <c r="W11" s="15"/>
-      <c r="AB11" s="4"/>
-      <c r="AC11" s="16"/>
-    </row>
-    <row r="12" spans="1:29" ht="23.1" customHeight="1">
-      <c r="A12" s="110"/>
-      <c r="B12" s="111"/>
-      <c r="C12" s="112"/>
-      <c r="D12" s="96"/>
-      <c r="E12" s="97"/>
-      <c r="F12" s="96"/>
-      <c r="G12" s="97"/>
-      <c r="H12" s="96"/>
-      <c r="I12" s="97"/>
-      <c r="J12" s="100"/>
-      <c r="K12" s="101"/>
-      <c r="L12" s="100"/>
-      <c r="M12" s="103"/>
-      <c r="N12" s="103"/>
-      <c r="O12" s="103"/>
-      <c r="P12" s="103"/>
-      <c r="Q12" s="103"/>
-      <c r="R12" s="103"/>
-      <c r="S12" s="103"/>
-      <c r="T12" s="103"/>
-      <c r="U12" s="103"/>
-      <c r="V12" s="101"/>
-      <c r="AB12" s="15"/>
-      <c r="AC12" s="16"/>
-    </row>
-    <row r="13" spans="1:29" ht="23.1" customHeight="1" thickBot="1">
-      <c r="A13" s="113" t="s">
+      <c r="M11" s="87"/>
+      <c r="N11" s="87"/>
+      <c r="O11" s="87"/>
+      <c r="P11" s="87"/>
+      <c r="Q11" s="87"/>
+      <c r="R11" s="87"/>
+      <c r="S11" s="87"/>
+      <c r="T11" s="87"/>
+      <c r="U11" s="87"/>
+      <c r="V11" s="84"/>
+    </row>
+    <row r="12" spans="1:22" ht="23.1" customHeight="1">
+      <c r="A12" s="95"/>
+      <c r="B12" s="96"/>
+      <c r="C12" s="97"/>
+      <c r="D12" s="81"/>
+      <c r="E12" s="82"/>
+      <c r="F12" s="81"/>
+      <c r="G12" s="82"/>
+      <c r="H12" s="81"/>
+      <c r="I12" s="82"/>
+      <c r="J12" s="85"/>
+      <c r="K12" s="86"/>
+      <c r="L12" s="85"/>
+      <c r="M12" s="88"/>
+      <c r="N12" s="88"/>
+      <c r="O12" s="88"/>
+      <c r="P12" s="88"/>
+      <c r="Q12" s="88"/>
+      <c r="R12" s="88"/>
+      <c r="S12" s="88"/>
+      <c r="T12" s="88"/>
+      <c r="U12" s="88"/>
+      <c r="V12" s="86"/>
+    </row>
+    <row r="13" spans="1:22" ht="23.1" customHeight="1" thickBot="1">
+      <c r="A13" s="98" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="114"/>
-      <c r="C13" s="114"/>
-      <c r="D13" s="115">
+      <c r="B13" s="99"/>
+      <c r="C13" s="99"/>
+      <c r="D13" s="100">
         <v>0.41666666666666669</v>
       </c>
-      <c r="E13" s="116"/>
-      <c r="F13" s="115">
+      <c r="E13" s="101"/>
+      <c r="F13" s="100">
         <v>0.79166666666666663</v>
       </c>
-      <c r="G13" s="116"/>
-      <c r="H13" s="119">
+      <c r="G13" s="101"/>
+      <c r="H13" s="104">
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="I13" s="120"/>
-      <c r="J13" s="115">
+      <c r="I13" s="105"/>
+      <c r="J13" s="100">
         <v>0.33333333333333331</v>
       </c>
-      <c r="K13" s="116"/>
-      <c r="L13" s="88" t="s">
+      <c r="K13" s="101"/>
+      <c r="L13" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="M13" s="89"/>
-      <c r="N13" s="89"/>
-      <c r="O13" s="89"/>
-      <c r="P13" s="89"/>
-      <c r="Q13" s="89"/>
-      <c r="R13" s="89"/>
-      <c r="S13" s="89"/>
-      <c r="T13" s="89"/>
-      <c r="U13" s="89"/>
-      <c r="V13" s="90"/>
-      <c r="W13" s="15"/>
-      <c r="X13" s="16"/>
-      <c r="AB13" s="4"/>
-    </row>
-    <row r="14" spans="1:29" ht="23.1" customHeight="1">
-      <c r="A14" s="117" t="str">
+      <c r="M13" s="74"/>
+      <c r="N13" s="74"/>
+      <c r="O13" s="74"/>
+      <c r="P13" s="74"/>
+      <c r="Q13" s="74"/>
+      <c r="R13" s="74"/>
+      <c r="S13" s="74"/>
+      <c r="T13" s="74"/>
+      <c r="U13" s="74"/>
+      <c r="V13" s="75"/>
+    </row>
+    <row r="14" spans="1:22" ht="23.1" customHeight="1">
+      <c r="A14" s="102" t="str">
         <f>IFERROR(VLOOKUP(A1,#REF!,2,0),"")</f>
         <v/>
       </c>
-      <c r="B14" s="118"/>
-      <c r="C14" s="11" t="str">
+      <c r="B14" s="103"/>
+      <c r="C14" s="8" t="str">
         <f>IF(A14="","", TEXT(A14,"aaa"))</f>
         <v/>
       </c>
-      <c r="D14" s="44"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="47"/>
-      <c r="H14" s="84"/>
-      <c r="I14" s="85"/>
-      <c r="J14" s="86" t="str">
+      <c r="D14" s="35"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="37"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="69"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="71" t="str">
         <f t="shared" ref="J14" si="0">IF(D14="","",(ABS(F14-D14))-H14)</f>
         <v/>
       </c>
-      <c r="K14" s="87"/>
-      <c r="L14" s="91"/>
-      <c r="M14" s="92"/>
-      <c r="N14" s="92"/>
-      <c r="O14" s="92"/>
-      <c r="P14" s="92"/>
-      <c r="Q14" s="92"/>
-      <c r="R14" s="92"/>
-      <c r="S14" s="92"/>
-      <c r="T14" s="92"/>
-      <c r="U14" s="92"/>
-      <c r="V14" s="93"/>
-      <c r="W14" s="14"/>
-      <c r="AB14" s="4"/>
-    </row>
-    <row r="15" spans="1:29" ht="23.1" customHeight="1">
-      <c r="A15" s="42" t="str">
+      <c r="K14" s="72"/>
+      <c r="L14" s="76"/>
+      <c r="M14" s="77"/>
+      <c r="N14" s="77"/>
+      <c r="O14" s="77"/>
+      <c r="P14" s="77"/>
+      <c r="Q14" s="77"/>
+      <c r="R14" s="77"/>
+      <c r="S14" s="77"/>
+      <c r="T14" s="77"/>
+      <c r="U14" s="77"/>
+      <c r="V14" s="78"/>
+    </row>
+    <row r="15" spans="1:22" ht="23.1" customHeight="1">
+      <c r="A15" s="33" t="str">
         <f>IF(A14="","",
 IF(OR(DAY(A14+1)&lt;=20, MONTH($A$14)=MONTH(A14+1)),A14+1,""))</f>
         <v/>
       </c>
-      <c r="B15" s="43"/>
-      <c r="C15" s="12" t="str">
+      <c r="B15" s="34"/>
+      <c r="C15" s="9" t="str">
         <f t="shared" ref="C15:C44" si="1">IF(A15="","", TEXT(A15,"aaa"))</f>
         <v/>
       </c>
-      <c r="D15" s="44"/>
-      <c r="E15" s="45"/>
-      <c r="F15" s="46"/>
-      <c r="G15" s="47"/>
-      <c r="H15" s="46"/>
-      <c r="I15" s="47"/>
-      <c r="J15" s="40" t="str">
+      <c r="D15" s="35"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="37"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="37"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="31" t="str">
         <f t="shared" ref="J15:J44" si="2">IF(D15="","",(ABS(F15-D15))-H15)</f>
         <v/>
       </c>
-      <c r="K15" s="41"/>
-      <c r="L15" s="37"/>
-      <c r="M15" s="38"/>
-      <c r="N15" s="38"/>
-      <c r="O15" s="38"/>
-      <c r="P15" s="38"/>
-      <c r="Q15" s="38"/>
-      <c r="R15" s="38"/>
-      <c r="S15" s="38"/>
-      <c r="T15" s="38"/>
-      <c r="U15" s="38"/>
-      <c r="V15" s="39"/>
-      <c r="W15" s="14"/>
-      <c r="AB15" s="4"/>
-    </row>
-    <row r="16" spans="1:29" ht="23.1" customHeight="1">
-      <c r="A16" s="42" t="str">
+      <c r="K15" s="32"/>
+      <c r="L15" s="28"/>
+      <c r="M15" s="29"/>
+      <c r="N15" s="29"/>
+      <c r="O15" s="29"/>
+      <c r="P15" s="29"/>
+      <c r="Q15" s="29"/>
+      <c r="R15" s="29"/>
+      <c r="S15" s="29"/>
+      <c r="T15" s="29"/>
+      <c r="U15" s="29"/>
+      <c r="V15" s="30"/>
+    </row>
+    <row r="16" spans="1:22" ht="23.1" customHeight="1">
+      <c r="A16" s="33" t="str">
         <f t="shared" ref="A16:A23" si="3">IF(A15="","",
 IF(OR(DAY(A15+1)&lt;=20, MONTH($A$14)=MONTH(A15+1)),A15+1,""))</f>
         <v/>
       </c>
-      <c r="B16" s="43"/>
-      <c r="C16" s="12" t="str">
+      <c r="B16" s="34"/>
+      <c r="C16" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="D16" s="44"/>
-      <c r="E16" s="45"/>
-      <c r="F16" s="46"/>
-      <c r="G16" s="47"/>
-      <c r="H16" s="46"/>
-      <c r="I16" s="47"/>
-      <c r="J16" s="40" t="str">
+      <c r="D16" s="35"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="37"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="37"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="31" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K16" s="41"/>
-      <c r="L16" s="37"/>
-      <c r="M16" s="38"/>
-      <c r="N16" s="38"/>
-      <c r="O16" s="38"/>
-      <c r="P16" s="38"/>
-      <c r="Q16" s="38"/>
-      <c r="R16" s="38"/>
-      <c r="S16" s="38"/>
-      <c r="T16" s="38"/>
-      <c r="U16" s="38"/>
-      <c r="V16" s="39"/>
-      <c r="W16" s="14"/>
-      <c r="AB16" s="4"/>
-    </row>
-    <row r="17" spans="1:28" ht="23.1" customHeight="1">
-      <c r="A17" s="42" t="str">
+      <c r="K16" s="32"/>
+      <c r="L16" s="28"/>
+      <c r="M16" s="29"/>
+      <c r="N16" s="29"/>
+      <c r="O16" s="29"/>
+      <c r="P16" s="29"/>
+      <c r="Q16" s="29"/>
+      <c r="R16" s="29"/>
+      <c r="S16" s="29"/>
+      <c r="T16" s="29"/>
+      <c r="U16" s="29"/>
+      <c r="V16" s="30"/>
+    </row>
+    <row r="17" spans="1:22" ht="23.1" customHeight="1">
+      <c r="A17" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="B17" s="43"/>
-      <c r="C17" s="12" t="str">
+      <c r="B17" s="34"/>
+      <c r="C17" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="D17" s="44"/>
-      <c r="E17" s="45"/>
-      <c r="F17" s="44"/>
-      <c r="G17" s="45"/>
-      <c r="H17" s="46"/>
-      <c r="I17" s="47"/>
-      <c r="J17" s="40" t="str">
+      <c r="D17" s="35"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="36"/>
+      <c r="H17" s="37"/>
+      <c r="I17" s="38"/>
+      <c r="J17" s="31" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K17" s="41"/>
-      <c r="L17" s="37"/>
-      <c r="M17" s="38"/>
-      <c r="N17" s="38"/>
-      <c r="O17" s="38"/>
-      <c r="P17" s="38"/>
-      <c r="Q17" s="38"/>
-      <c r="R17" s="38"/>
-      <c r="S17" s="38"/>
-      <c r="T17" s="38"/>
-      <c r="U17" s="38"/>
-      <c r="V17" s="39"/>
-      <c r="W17" s="14"/>
-      <c r="AB17" s="4"/>
-    </row>
-    <row r="18" spans="1:28" ht="23.1" customHeight="1">
-      <c r="A18" s="42" t="str">
+      <c r="K17" s="32"/>
+      <c r="L17" s="28"/>
+      <c r="M17" s="29"/>
+      <c r="N17" s="29"/>
+      <c r="O17" s="29"/>
+      <c r="P17" s="29"/>
+      <c r="Q17" s="29"/>
+      <c r="R17" s="29"/>
+      <c r="S17" s="29"/>
+      <c r="T17" s="29"/>
+      <c r="U17" s="29"/>
+      <c r="V17" s="30"/>
+    </row>
+    <row r="18" spans="1:22" ht="23.1" customHeight="1">
+      <c r="A18" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="B18" s="43"/>
-      <c r="C18" s="12" t="str">
+      <c r="B18" s="34"/>
+      <c r="C18" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="D18" s="44"/>
-      <c r="E18" s="45"/>
-      <c r="F18" s="44"/>
-      <c r="G18" s="45"/>
-      <c r="H18" s="46"/>
-      <c r="I18" s="47"/>
-      <c r="J18" s="40" t="str">
+      <c r="D18" s="35"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="36"/>
+      <c r="H18" s="37"/>
+      <c r="I18" s="38"/>
+      <c r="J18" s="31" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K18" s="41"/>
-      <c r="L18" s="37"/>
-      <c r="M18" s="38"/>
-      <c r="N18" s="38"/>
-      <c r="O18" s="38"/>
-      <c r="P18" s="38"/>
-      <c r="Q18" s="38"/>
-      <c r="R18" s="38"/>
-      <c r="S18" s="38"/>
-      <c r="T18" s="38"/>
-      <c r="U18" s="38"/>
-      <c r="V18" s="39"/>
-      <c r="W18" s="14"/>
-      <c r="AB18" s="4"/>
-    </row>
-    <row r="19" spans="1:28" ht="23.1" customHeight="1">
-      <c r="A19" s="42" t="str">
+      <c r="K18" s="32"/>
+      <c r="L18" s="28"/>
+      <c r="M18" s="29"/>
+      <c r="N18" s="29"/>
+      <c r="O18" s="29"/>
+      <c r="P18" s="29"/>
+      <c r="Q18" s="29"/>
+      <c r="R18" s="29"/>
+      <c r="S18" s="29"/>
+      <c r="T18" s="29"/>
+      <c r="U18" s="29"/>
+      <c r="V18" s="30"/>
+    </row>
+    <row r="19" spans="1:22" ht="23.1" customHeight="1">
+      <c r="A19" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="B19" s="43"/>
-      <c r="C19" s="12" t="str">
+      <c r="B19" s="34"/>
+      <c r="C19" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="D19" s="44"/>
-      <c r="E19" s="45"/>
-      <c r="F19" s="46"/>
-      <c r="G19" s="47"/>
-      <c r="H19" s="46"/>
-      <c r="I19" s="47"/>
-      <c r="J19" s="40" t="str">
+      <c r="D19" s="35"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="37"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="37"/>
+      <c r="I19" s="38"/>
+      <c r="J19" s="31" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K19" s="41"/>
-      <c r="L19" s="37"/>
-      <c r="M19" s="38"/>
-      <c r="N19" s="38"/>
-      <c r="O19" s="38"/>
-      <c r="P19" s="38"/>
-      <c r="Q19" s="38"/>
-      <c r="R19" s="38"/>
-      <c r="S19" s="38"/>
-      <c r="T19" s="38"/>
-      <c r="U19" s="38"/>
-      <c r="V19" s="39"/>
-      <c r="W19" s="14"/>
-      <c r="AB19" s="4"/>
-    </row>
-    <row r="20" spans="1:28" ht="23.1" customHeight="1">
-      <c r="A20" s="42" t="str">
+      <c r="K19" s="32"/>
+      <c r="L19" s="28"/>
+      <c r="M19" s="29"/>
+      <c r="N19" s="29"/>
+      <c r="O19" s="29"/>
+      <c r="P19" s="29"/>
+      <c r="Q19" s="29"/>
+      <c r="R19" s="29"/>
+      <c r="S19" s="29"/>
+      <c r="T19" s="29"/>
+      <c r="U19" s="29"/>
+      <c r="V19" s="30"/>
+    </row>
+    <row r="20" spans="1:22" ht="23.1" customHeight="1">
+      <c r="A20" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="B20" s="43"/>
-      <c r="C20" s="12" t="str">
+      <c r="B20" s="34"/>
+      <c r="C20" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="D20" s="44"/>
-      <c r="E20" s="45"/>
-      <c r="F20" s="46"/>
-      <c r="G20" s="47"/>
-      <c r="H20" s="46"/>
-      <c r="I20" s="47"/>
-      <c r="J20" s="40" t="str">
+      <c r="D20" s="35"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="37"/>
+      <c r="G20" s="38"/>
+      <c r="H20" s="37"/>
+      <c r="I20" s="38"/>
+      <c r="J20" s="31" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K20" s="41"/>
-      <c r="L20" s="37"/>
-      <c r="M20" s="38"/>
-      <c r="N20" s="38"/>
-      <c r="O20" s="38"/>
-      <c r="P20" s="38"/>
-      <c r="Q20" s="38"/>
-      <c r="R20" s="38"/>
-      <c r="S20" s="38"/>
-      <c r="T20" s="38"/>
-      <c r="U20" s="38"/>
-      <c r="V20" s="39"/>
-      <c r="W20" s="14"/>
-      <c r="AB20" s="4"/>
-    </row>
-    <row r="21" spans="1:28" ht="23.1" customHeight="1">
-      <c r="A21" s="42" t="str">
+      <c r="K20" s="32"/>
+      <c r="L20" s="28"/>
+      <c r="M20" s="29"/>
+      <c r="N20" s="29"/>
+      <c r="O20" s="29"/>
+      <c r="P20" s="29"/>
+      <c r="Q20" s="29"/>
+      <c r="R20" s="29"/>
+      <c r="S20" s="29"/>
+      <c r="T20" s="29"/>
+      <c r="U20" s="29"/>
+      <c r="V20" s="30"/>
+    </row>
+    <row r="21" spans="1:22" ht="23.1" customHeight="1">
+      <c r="A21" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="B21" s="43"/>
-      <c r="C21" s="12" t="str">
+      <c r="B21" s="34"/>
+      <c r="C21" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="D21" s="44"/>
-      <c r="E21" s="45"/>
-      <c r="F21" s="46"/>
-      <c r="G21" s="47"/>
-      <c r="H21" s="46"/>
-      <c r="I21" s="47"/>
-      <c r="J21" s="40" t="str">
+      <c r="D21" s="35"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="37"/>
+      <c r="G21" s="38"/>
+      <c r="H21" s="37"/>
+      <c r="I21" s="38"/>
+      <c r="J21" s="31" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K21" s="41"/>
-      <c r="L21" s="37"/>
-      <c r="M21" s="38"/>
-      <c r="N21" s="38"/>
-      <c r="O21" s="38"/>
-      <c r="P21" s="38"/>
-      <c r="Q21" s="38"/>
-      <c r="R21" s="38"/>
-      <c r="S21" s="38"/>
-      <c r="T21" s="38"/>
-      <c r="U21" s="38"/>
-      <c r="V21" s="39"/>
-      <c r="W21" s="14"/>
-      <c r="AB21" s="4"/>
-    </row>
-    <row r="22" spans="1:28" ht="23.1" customHeight="1">
-      <c r="A22" s="42" t="str">
+      <c r="K21" s="32"/>
+      <c r="L21" s="28"/>
+      <c r="M21" s="29"/>
+      <c r="N21" s="29"/>
+      <c r="O21" s="29"/>
+      <c r="P21" s="29"/>
+      <c r="Q21" s="29"/>
+      <c r="R21" s="29"/>
+      <c r="S21" s="29"/>
+      <c r="T21" s="29"/>
+      <c r="U21" s="29"/>
+      <c r="V21" s="30"/>
+    </row>
+    <row r="22" spans="1:22" ht="23.1" customHeight="1">
+      <c r="A22" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="B22" s="43"/>
-      <c r="C22" s="12" t="str">
+      <c r="B22" s="34"/>
+      <c r="C22" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="D22" s="44"/>
-      <c r="E22" s="45"/>
-      <c r="F22" s="46"/>
-      <c r="G22" s="47"/>
-      <c r="H22" s="46"/>
-      <c r="I22" s="47"/>
-      <c r="J22" s="40" t="str">
+      <c r="D22" s="35"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="37"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="37"/>
+      <c r="I22" s="38"/>
+      <c r="J22" s="31" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K22" s="41"/>
-      <c r="L22" s="37"/>
-      <c r="M22" s="38"/>
-      <c r="N22" s="38"/>
-      <c r="O22" s="38"/>
-      <c r="P22" s="38"/>
-      <c r="Q22" s="38"/>
-      <c r="R22" s="38"/>
-      <c r="S22" s="38"/>
-      <c r="T22" s="38"/>
-      <c r="U22" s="38"/>
-      <c r="V22" s="39"/>
-      <c r="W22" s="14"/>
-      <c r="AB22" s="4"/>
-    </row>
-    <row r="23" spans="1:28" ht="23.1" customHeight="1">
-      <c r="A23" s="42" t="str">
+      <c r="K22" s="32"/>
+      <c r="L22" s="28"/>
+      <c r="M22" s="29"/>
+      <c r="N22" s="29"/>
+      <c r="O22" s="29"/>
+      <c r="P22" s="29"/>
+      <c r="Q22" s="29"/>
+      <c r="R22" s="29"/>
+      <c r="S22" s="29"/>
+      <c r="T22" s="29"/>
+      <c r="U22" s="29"/>
+      <c r="V22" s="30"/>
+    </row>
+    <row r="23" spans="1:22" ht="23.1" customHeight="1">
+      <c r="A23" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="B23" s="43"/>
-      <c r="C23" s="12" t="str">
+      <c r="B23" s="34"/>
+      <c r="C23" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="D23" s="44"/>
-      <c r="E23" s="45"/>
-      <c r="F23" s="46"/>
-      <c r="G23" s="47"/>
-      <c r="H23" s="46"/>
-      <c r="I23" s="47"/>
-      <c r="J23" s="40" t="str">
+      <c r="D23" s="35"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="37"/>
+      <c r="G23" s="38"/>
+      <c r="H23" s="37"/>
+      <c r="I23" s="38"/>
+      <c r="J23" s="31" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K23" s="41"/>
-      <c r="L23" s="37"/>
-      <c r="M23" s="38"/>
-      <c r="N23" s="38"/>
-      <c r="O23" s="38"/>
-      <c r="P23" s="38"/>
-      <c r="Q23" s="38"/>
-      <c r="R23" s="38"/>
-      <c r="S23" s="38"/>
-      <c r="T23" s="38"/>
-      <c r="U23" s="38"/>
-      <c r="V23" s="39"/>
-      <c r="W23" s="14"/>
-      <c r="AB23" s="4"/>
-    </row>
-    <row r="24" spans="1:28" ht="23.1" customHeight="1">
-      <c r="A24" s="42" t="str">
+      <c r="K23" s="32"/>
+      <c r="L23" s="28"/>
+      <c r="M23" s="29"/>
+      <c r="N23" s="29"/>
+      <c r="O23" s="29"/>
+      <c r="P23" s="29"/>
+      <c r="Q23" s="29"/>
+      <c r="R23" s="29"/>
+      <c r="S23" s="29"/>
+      <c r="T23" s="29"/>
+      <c r="U23" s="29"/>
+      <c r="V23" s="30"/>
+    </row>
+    <row r="24" spans="1:22" ht="23.1" customHeight="1">
+      <c r="A24" s="33" t="str">
         <f t="shared" ref="A24:A35" si="4">IF(A23="","",
 IF(OR(DAY(A23+1)&lt;=20, MONTH($A$14)=MONTH(A23+1)),A23+1,""))</f>
         <v/>
       </c>
-      <c r="B24" s="43"/>
-      <c r="C24" s="12" t="str">
+      <c r="B24" s="34"/>
+      <c r="C24" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="D24" s="46"/>
-      <c r="E24" s="47"/>
-      <c r="F24" s="46"/>
-      <c r="G24" s="47"/>
-      <c r="H24" s="46"/>
-      <c r="I24" s="47"/>
-      <c r="J24" s="40" t="str">
+      <c r="D24" s="37"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="37"/>
+      <c r="G24" s="38"/>
+      <c r="H24" s="37"/>
+      <c r="I24" s="38"/>
+      <c r="J24" s="31" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K24" s="41"/>
-      <c r="L24" s="37"/>
-      <c r="M24" s="38"/>
-      <c r="N24" s="38"/>
-      <c r="O24" s="38"/>
-      <c r="P24" s="38"/>
-      <c r="Q24" s="38"/>
-      <c r="R24" s="38"/>
-      <c r="S24" s="38"/>
-      <c r="T24" s="38"/>
-      <c r="U24" s="38"/>
-      <c r="V24" s="39"/>
-      <c r="W24" s="14"/>
-      <c r="AB24" s="4"/>
-    </row>
-    <row r="25" spans="1:28" ht="23.1" customHeight="1">
-      <c r="A25" s="42" t="str">
+      <c r="K24" s="32"/>
+      <c r="L24" s="28"/>
+      <c r="M24" s="29"/>
+      <c r="N24" s="29"/>
+      <c r="O24" s="29"/>
+      <c r="P24" s="29"/>
+      <c r="Q24" s="29"/>
+      <c r="R24" s="29"/>
+      <c r="S24" s="29"/>
+      <c r="T24" s="29"/>
+      <c r="U24" s="29"/>
+      <c r="V24" s="30"/>
+    </row>
+    <row r="25" spans="1:22" ht="23.1" customHeight="1">
+      <c r="A25" s="33" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="B25" s="43"/>
-      <c r="C25" s="12" t="str">
+      <c r="B25" s="34"/>
+      <c r="C25" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="D25" s="46"/>
-      <c r="E25" s="47"/>
-      <c r="F25" s="46"/>
-      <c r="G25" s="47"/>
-      <c r="H25" s="46"/>
-      <c r="I25" s="47"/>
-      <c r="J25" s="40" t="str">
+      <c r="D25" s="37"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="37"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="37"/>
+      <c r="I25" s="38"/>
+      <c r="J25" s="31" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K25" s="41"/>
-      <c r="L25" s="37"/>
-      <c r="M25" s="38"/>
-      <c r="N25" s="38"/>
-      <c r="O25" s="38"/>
-      <c r="P25" s="38"/>
-      <c r="Q25" s="38"/>
-      <c r="R25" s="38"/>
-      <c r="S25" s="38"/>
-      <c r="T25" s="38"/>
-      <c r="U25" s="38"/>
-      <c r="V25" s="39"/>
-      <c r="W25" s="14"/>
-      <c r="AB25" s="4"/>
-    </row>
-    <row r="26" spans="1:28" ht="23.1" customHeight="1">
-      <c r="A26" s="42" t="str">
+      <c r="K25" s="32"/>
+      <c r="L25" s="28"/>
+      <c r="M25" s="29"/>
+      <c r="N25" s="29"/>
+      <c r="O25" s="29"/>
+      <c r="P25" s="29"/>
+      <c r="Q25" s="29"/>
+      <c r="R25" s="29"/>
+      <c r="S25" s="29"/>
+      <c r="T25" s="29"/>
+      <c r="U25" s="29"/>
+      <c r="V25" s="30"/>
+    </row>
+    <row r="26" spans="1:22" ht="23.1" customHeight="1">
+      <c r="A26" s="33" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="B26" s="43"/>
-      <c r="C26" s="12" t="str">
+      <c r="B26" s="34"/>
+      <c r="C26" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="D26" s="44"/>
-      <c r="E26" s="45"/>
-      <c r="F26" s="46"/>
-      <c r="G26" s="47"/>
-      <c r="H26" s="46"/>
-      <c r="I26" s="47"/>
-      <c r="J26" s="40" t="str">
+      <c r="D26" s="35"/>
+      <c r="E26" s="36"/>
+      <c r="F26" s="37"/>
+      <c r="G26" s="38"/>
+      <c r="H26" s="37"/>
+      <c r="I26" s="38"/>
+      <c r="J26" s="31" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K26" s="41"/>
-      <c r="L26" s="37"/>
-      <c r="M26" s="38"/>
-      <c r="N26" s="38"/>
-      <c r="O26" s="38"/>
-      <c r="P26" s="38"/>
-      <c r="Q26" s="38"/>
-      <c r="R26" s="38"/>
-      <c r="S26" s="38"/>
-      <c r="T26" s="38"/>
-      <c r="U26" s="38"/>
-      <c r="V26" s="39"/>
-      <c r="W26" s="14"/>
-      <c r="AB26" s="4"/>
-    </row>
-    <row r="27" spans="1:28" ht="23.1" customHeight="1">
-      <c r="A27" s="42" t="str">
+      <c r="K26" s="32"/>
+      <c r="L26" s="28"/>
+      <c r="M26" s="29"/>
+      <c r="N26" s="29"/>
+      <c r="O26" s="29"/>
+      <c r="P26" s="29"/>
+      <c r="Q26" s="29"/>
+      <c r="R26" s="29"/>
+      <c r="S26" s="29"/>
+      <c r="T26" s="29"/>
+      <c r="U26" s="29"/>
+      <c r="V26" s="30"/>
+    </row>
+    <row r="27" spans="1:22" ht="23.1" customHeight="1">
+      <c r="A27" s="33" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="B27" s="43"/>
-      <c r="C27" s="12" t="str">
+      <c r="B27" s="34"/>
+      <c r="C27" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="D27" s="44"/>
-      <c r="E27" s="45"/>
-      <c r="F27" s="46"/>
-      <c r="G27" s="47"/>
-      <c r="H27" s="46"/>
-      <c r="I27" s="47"/>
-      <c r="J27" s="40" t="str">
+      <c r="D27" s="35"/>
+      <c r="E27" s="36"/>
+      <c r="F27" s="37"/>
+      <c r="G27" s="38"/>
+      <c r="H27" s="37"/>
+      <c r="I27" s="38"/>
+      <c r="J27" s="31" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K27" s="41"/>
-      <c r="L27" s="37"/>
-      <c r="M27" s="38"/>
-      <c r="N27" s="38"/>
-      <c r="O27" s="38"/>
-      <c r="P27" s="38"/>
-      <c r="Q27" s="38"/>
-      <c r="R27" s="38"/>
-      <c r="S27" s="38"/>
-      <c r="T27" s="38"/>
-      <c r="U27" s="38"/>
-      <c r="V27" s="39"/>
-      <c r="W27" s="14"/>
-      <c r="AB27" s="4"/>
-    </row>
-    <row r="28" spans="1:28" ht="23.1" customHeight="1">
-      <c r="A28" s="42" t="str">
+      <c r="K27" s="32"/>
+      <c r="L27" s="28"/>
+      <c r="M27" s="29"/>
+      <c r="N27" s="29"/>
+      <c r="O27" s="29"/>
+      <c r="P27" s="29"/>
+      <c r="Q27" s="29"/>
+      <c r="R27" s="29"/>
+      <c r="S27" s="29"/>
+      <c r="T27" s="29"/>
+      <c r="U27" s="29"/>
+      <c r="V27" s="30"/>
+    </row>
+    <row r="28" spans="1:22" ht="23.1" customHeight="1">
+      <c r="A28" s="33" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="B28" s="43"/>
-      <c r="C28" s="12" t="str">
+      <c r="B28" s="34"/>
+      <c r="C28" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="D28" s="44"/>
-      <c r="E28" s="45"/>
-      <c r="F28" s="46"/>
-      <c r="G28" s="47"/>
-      <c r="H28" s="46"/>
-      <c r="I28" s="47"/>
-      <c r="J28" s="40" t="str">
+      <c r="D28" s="35"/>
+      <c r="E28" s="36"/>
+      <c r="F28" s="37"/>
+      <c r="G28" s="38"/>
+      <c r="H28" s="37"/>
+      <c r="I28" s="38"/>
+      <c r="J28" s="31" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K28" s="41"/>
-      <c r="L28" s="37"/>
-      <c r="M28" s="38"/>
-      <c r="N28" s="38"/>
-      <c r="O28" s="38"/>
-      <c r="P28" s="38"/>
-      <c r="Q28" s="38"/>
-      <c r="R28" s="38"/>
-      <c r="S28" s="38"/>
-      <c r="T28" s="38"/>
-      <c r="U28" s="38"/>
-      <c r="V28" s="39"/>
-      <c r="W28" s="14"/>
-      <c r="AB28" s="4"/>
-    </row>
-    <row r="29" spans="1:28" ht="23.1" customHeight="1">
-      <c r="A29" s="42" t="str">
+      <c r="K28" s="32"/>
+      <c r="L28" s="28"/>
+      <c r="M28" s="29"/>
+      <c r="N28" s="29"/>
+      <c r="O28" s="29"/>
+      <c r="P28" s="29"/>
+      <c r="Q28" s="29"/>
+      <c r="R28" s="29"/>
+      <c r="S28" s="29"/>
+      <c r="T28" s="29"/>
+      <c r="U28" s="29"/>
+      <c r="V28" s="30"/>
+    </row>
+    <row r="29" spans="1:22" ht="23.1" customHeight="1">
+      <c r="A29" s="33" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="B29" s="43"/>
-      <c r="C29" s="12" t="str">
+      <c r="B29" s="34"/>
+      <c r="C29" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="D29" s="44"/>
-      <c r="E29" s="45"/>
-      <c r="F29" s="46"/>
-      <c r="G29" s="47"/>
-      <c r="H29" s="46"/>
-      <c r="I29" s="47"/>
-      <c r="J29" s="40" t="str">
+      <c r="D29" s="35"/>
+      <c r="E29" s="36"/>
+      <c r="F29" s="37"/>
+      <c r="G29" s="38"/>
+      <c r="H29" s="37"/>
+      <c r="I29" s="38"/>
+      <c r="J29" s="31" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K29" s="41"/>
-      <c r="L29" s="37"/>
-      <c r="M29" s="38"/>
-      <c r="N29" s="38"/>
-      <c r="O29" s="38"/>
-      <c r="P29" s="38"/>
-      <c r="Q29" s="38"/>
-      <c r="R29" s="38"/>
-      <c r="S29" s="38"/>
-      <c r="T29" s="38"/>
-      <c r="U29" s="38"/>
-      <c r="V29" s="39"/>
-      <c r="W29" s="14"/>
-      <c r="AB29" s="4"/>
-    </row>
-    <row r="30" spans="1:28" ht="23.1" customHeight="1">
-      <c r="A30" s="42" t="str">
+      <c r="K29" s="32"/>
+      <c r="L29" s="28"/>
+      <c r="M29" s="29"/>
+      <c r="N29" s="29"/>
+      <c r="O29" s="29"/>
+      <c r="P29" s="29"/>
+      <c r="Q29" s="29"/>
+      <c r="R29" s="29"/>
+      <c r="S29" s="29"/>
+      <c r="T29" s="29"/>
+      <c r="U29" s="29"/>
+      <c r="V29" s="30"/>
+    </row>
+    <row r="30" spans="1:22" ht="23.1" customHeight="1">
+      <c r="A30" s="33" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="B30" s="43"/>
-      <c r="C30" s="12" t="str">
+      <c r="B30" s="34"/>
+      <c r="C30" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="D30" s="44"/>
-      <c r="E30" s="45"/>
-      <c r="F30" s="46"/>
-      <c r="G30" s="47"/>
-      <c r="H30" s="46"/>
-      <c r="I30" s="47"/>
-      <c r="J30" s="40" t="str">
+      <c r="D30" s="35"/>
+      <c r="E30" s="36"/>
+      <c r="F30" s="37"/>
+      <c r="G30" s="38"/>
+      <c r="H30" s="37"/>
+      <c r="I30" s="38"/>
+      <c r="J30" s="31" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K30" s="41"/>
-      <c r="L30" s="37"/>
-      <c r="M30" s="38"/>
-      <c r="N30" s="38"/>
-      <c r="O30" s="38"/>
-      <c r="P30" s="38"/>
-      <c r="Q30" s="38"/>
-      <c r="R30" s="38"/>
-      <c r="S30" s="38"/>
-      <c r="T30" s="38"/>
-      <c r="U30" s="38"/>
-      <c r="V30" s="39"/>
-      <c r="W30" s="14"/>
-      <c r="AB30" s="4"/>
-    </row>
-    <row r="31" spans="1:28" ht="23.1" customHeight="1">
-      <c r="A31" s="42" t="str">
+      <c r="K30" s="32"/>
+      <c r="L30" s="28"/>
+      <c r="M30" s="29"/>
+      <c r="N30" s="29"/>
+      <c r="O30" s="29"/>
+      <c r="P30" s="29"/>
+      <c r="Q30" s="29"/>
+      <c r="R30" s="29"/>
+      <c r="S30" s="29"/>
+      <c r="T30" s="29"/>
+      <c r="U30" s="29"/>
+      <c r="V30" s="30"/>
+    </row>
+    <row r="31" spans="1:22" ht="23.1" customHeight="1">
+      <c r="A31" s="33" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="B31" s="43"/>
-      <c r="C31" s="12" t="str">
+      <c r="B31" s="34"/>
+      <c r="C31" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="D31" s="46"/>
-      <c r="E31" s="47"/>
-      <c r="F31" s="46"/>
-      <c r="G31" s="47"/>
-      <c r="H31" s="46"/>
-      <c r="I31" s="47"/>
-      <c r="J31" s="40" t="str">
+      <c r="D31" s="37"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="37"/>
+      <c r="G31" s="38"/>
+      <c r="H31" s="37"/>
+      <c r="I31" s="38"/>
+      <c r="J31" s="31" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K31" s="41"/>
-      <c r="L31" s="37"/>
-      <c r="M31" s="38"/>
-      <c r="N31" s="38"/>
-      <c r="O31" s="38"/>
-      <c r="P31" s="38"/>
-      <c r="Q31" s="38"/>
-      <c r="R31" s="38"/>
-      <c r="S31" s="38"/>
-      <c r="T31" s="38"/>
-      <c r="U31" s="38"/>
-      <c r="V31" s="39"/>
-      <c r="W31" s="14"/>
-      <c r="AB31" s="4"/>
-    </row>
-    <row r="32" spans="1:28" ht="23.1" customHeight="1">
-      <c r="A32" s="42" t="str">
+      <c r="K31" s="32"/>
+      <c r="L31" s="28"/>
+      <c r="M31" s="29"/>
+      <c r="N31" s="29"/>
+      <c r="O31" s="29"/>
+      <c r="P31" s="29"/>
+      <c r="Q31" s="29"/>
+      <c r="R31" s="29"/>
+      <c r="S31" s="29"/>
+      <c r="T31" s="29"/>
+      <c r="U31" s="29"/>
+      <c r="V31" s="30"/>
+    </row>
+    <row r="32" spans="1:22" ht="23.1" customHeight="1">
+      <c r="A32" s="33" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="B32" s="43"/>
-      <c r="C32" s="12" t="str">
+      <c r="B32" s="34"/>
+      <c r="C32" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="D32" s="46"/>
-      <c r="E32" s="47"/>
-      <c r="F32" s="46"/>
-      <c r="G32" s="47"/>
-      <c r="H32" s="46"/>
-      <c r="I32" s="47"/>
-      <c r="J32" s="40" t="str">
+      <c r="D32" s="37"/>
+      <c r="E32" s="38"/>
+      <c r="F32" s="37"/>
+      <c r="G32" s="38"/>
+      <c r="H32" s="37"/>
+      <c r="I32" s="38"/>
+      <c r="J32" s="31" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K32" s="41"/>
-      <c r="L32" s="37"/>
-      <c r="M32" s="38"/>
-      <c r="N32" s="38"/>
-      <c r="O32" s="38"/>
-      <c r="P32" s="38"/>
-      <c r="Q32" s="38"/>
-      <c r="R32" s="38"/>
-      <c r="S32" s="38"/>
-      <c r="T32" s="38"/>
-      <c r="U32" s="38"/>
-      <c r="V32" s="39"/>
-      <c r="W32" s="14"/>
-      <c r="AB32" s="4"/>
-    </row>
-    <row r="33" spans="1:28" ht="23.1" customHeight="1">
-      <c r="A33" s="42" t="str">
+      <c r="K32" s="32"/>
+      <c r="L32" s="28"/>
+      <c r="M32" s="29"/>
+      <c r="N32" s="29"/>
+      <c r="O32" s="29"/>
+      <c r="P32" s="29"/>
+      <c r="Q32" s="29"/>
+      <c r="R32" s="29"/>
+      <c r="S32" s="29"/>
+      <c r="T32" s="29"/>
+      <c r="U32" s="29"/>
+      <c r="V32" s="30"/>
+    </row>
+    <row r="33" spans="1:22" ht="23.1" customHeight="1">
+      <c r="A33" s="33" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="B33" s="43"/>
-      <c r="C33" s="12" t="str">
+      <c r="B33" s="34"/>
+      <c r="C33" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="D33" s="46"/>
-      <c r="E33" s="47"/>
-      <c r="F33" s="46"/>
-      <c r="G33" s="47"/>
-      <c r="H33" s="46"/>
-      <c r="I33" s="47"/>
-      <c r="J33" s="40" t="str">
+      <c r="D33" s="37"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="37"/>
+      <c r="G33" s="38"/>
+      <c r="H33" s="37"/>
+      <c r="I33" s="38"/>
+      <c r="J33" s="31" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K33" s="41"/>
-      <c r="L33" s="37"/>
-      <c r="M33" s="38"/>
-      <c r="N33" s="38"/>
-      <c r="O33" s="38"/>
-      <c r="P33" s="38"/>
-      <c r="Q33" s="38"/>
-      <c r="R33" s="38"/>
-      <c r="S33" s="38"/>
-      <c r="T33" s="38"/>
-      <c r="U33" s="38"/>
-      <c r="V33" s="39"/>
-      <c r="W33" s="14"/>
-      <c r="AB33" s="4"/>
-    </row>
-    <row r="34" spans="1:28" ht="23.1" customHeight="1">
-      <c r="A34" s="42" t="str">
+      <c r="K33" s="32"/>
+      <c r="L33" s="28"/>
+      <c r="M33" s="29"/>
+      <c r="N33" s="29"/>
+      <c r="O33" s="29"/>
+      <c r="P33" s="29"/>
+      <c r="Q33" s="29"/>
+      <c r="R33" s="29"/>
+      <c r="S33" s="29"/>
+      <c r="T33" s="29"/>
+      <c r="U33" s="29"/>
+      <c r="V33" s="30"/>
+    </row>
+    <row r="34" spans="1:22" ht="23.1" customHeight="1">
+      <c r="A34" s="33" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="B34" s="43"/>
-      <c r="C34" s="12" t="str">
+      <c r="B34" s="34"/>
+      <c r="C34" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="D34" s="44"/>
-      <c r="E34" s="45"/>
-      <c r="F34" s="46"/>
-      <c r="G34" s="47"/>
-      <c r="H34" s="46"/>
-      <c r="I34" s="47"/>
-      <c r="J34" s="40" t="str">
+      <c r="D34" s="35"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="37"/>
+      <c r="G34" s="38"/>
+      <c r="H34" s="37"/>
+      <c r="I34" s="38"/>
+      <c r="J34" s="31" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K34" s="41"/>
-      <c r="L34" s="37"/>
-      <c r="M34" s="38"/>
-      <c r="N34" s="38"/>
-      <c r="O34" s="38"/>
-      <c r="P34" s="38"/>
-      <c r="Q34" s="38"/>
-      <c r="R34" s="38"/>
-      <c r="S34" s="38"/>
-      <c r="T34" s="38"/>
-      <c r="U34" s="38"/>
-      <c r="V34" s="39"/>
-      <c r="W34" s="14"/>
-      <c r="AB34" s="4"/>
-    </row>
-    <row r="35" spans="1:28" ht="23.1" customHeight="1">
-      <c r="A35" s="42" t="str">
+      <c r="K34" s="32"/>
+      <c r="L34" s="28"/>
+      <c r="M34" s="29"/>
+      <c r="N34" s="29"/>
+      <c r="O34" s="29"/>
+      <c r="P34" s="29"/>
+      <c r="Q34" s="29"/>
+      <c r="R34" s="29"/>
+      <c r="S34" s="29"/>
+      <c r="T34" s="29"/>
+      <c r="U34" s="29"/>
+      <c r="V34" s="30"/>
+    </row>
+    <row r="35" spans="1:22" ht="23.1" customHeight="1">
+      <c r="A35" s="33" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="B35" s="43"/>
-      <c r="C35" s="12" t="str">
+      <c r="B35" s="34"/>
+      <c r="C35" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="D35" s="44"/>
-      <c r="E35" s="45"/>
-      <c r="F35" s="46"/>
-      <c r="G35" s="47"/>
-      <c r="H35" s="46"/>
-      <c r="I35" s="47"/>
-      <c r="J35" s="40" t="str">
+      <c r="D35" s="35"/>
+      <c r="E35" s="36"/>
+      <c r="F35" s="37"/>
+      <c r="G35" s="38"/>
+      <c r="H35" s="37"/>
+      <c r="I35" s="38"/>
+      <c r="J35" s="31" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K35" s="41"/>
-      <c r="L35" s="37"/>
-      <c r="M35" s="38"/>
-      <c r="N35" s="38"/>
-      <c r="O35" s="38"/>
-      <c r="P35" s="38"/>
-      <c r="Q35" s="38"/>
-      <c r="R35" s="38"/>
-      <c r="S35" s="38"/>
-      <c r="T35" s="38"/>
-      <c r="U35" s="38"/>
-      <c r="V35" s="39"/>
-      <c r="W35" s="14"/>
-      <c r="AB35" s="4"/>
-    </row>
-    <row r="36" spans="1:28" ht="23.1" customHeight="1">
-      <c r="A36" s="42" t="str">
+      <c r="K35" s="32"/>
+      <c r="L35" s="28"/>
+      <c r="M35" s="29"/>
+      <c r="N35" s="29"/>
+      <c r="O35" s="29"/>
+      <c r="P35" s="29"/>
+      <c r="Q35" s="29"/>
+      <c r="R35" s="29"/>
+      <c r="S35" s="29"/>
+      <c r="T35" s="29"/>
+      <c r="U35" s="29"/>
+      <c r="V35" s="30"/>
+    </row>
+    <row r="36" spans="1:22" ht="23.1" customHeight="1">
+      <c r="A36" s="33" t="str">
         <f t="shared" ref="A36:A44" si="5">IF(A35="","",
 IF(OR(DAY(A35+1)&lt;=20, MONTH($A$14)=MONTH(A35+1)),A35+1,""))</f>
         <v/>
       </c>
-      <c r="B36" s="43"/>
-      <c r="C36" s="12" t="str">
+      <c r="B36" s="34"/>
+      <c r="C36" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="D36" s="44"/>
-      <c r="E36" s="45"/>
-      <c r="F36" s="46"/>
-      <c r="G36" s="47"/>
-      <c r="H36" s="46"/>
-      <c r="I36" s="47"/>
-      <c r="J36" s="40" t="str">
+      <c r="D36" s="35"/>
+      <c r="E36" s="36"/>
+      <c r="F36" s="37"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="37"/>
+      <c r="I36" s="38"/>
+      <c r="J36" s="31" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K36" s="41"/>
-      <c r="L36" s="37"/>
-      <c r="M36" s="38"/>
-      <c r="N36" s="38"/>
-      <c r="O36" s="38"/>
-      <c r="P36" s="38"/>
-      <c r="Q36" s="38"/>
-      <c r="R36" s="38"/>
-      <c r="S36" s="38"/>
-      <c r="T36" s="38"/>
-      <c r="U36" s="38"/>
-      <c r="V36" s="39"/>
-      <c r="W36" s="14"/>
-      <c r="AB36" s="4"/>
-    </row>
-    <row r="37" spans="1:28" ht="23.1" customHeight="1">
-      <c r="A37" s="42" t="str">
+      <c r="K36" s="32"/>
+      <c r="L36" s="28"/>
+      <c r="M36" s="29"/>
+      <c r="N36" s="29"/>
+      <c r="O36" s="29"/>
+      <c r="P36" s="29"/>
+      <c r="Q36" s="29"/>
+      <c r="R36" s="29"/>
+      <c r="S36" s="29"/>
+      <c r="T36" s="29"/>
+      <c r="U36" s="29"/>
+      <c r="V36" s="30"/>
+    </row>
+    <row r="37" spans="1:22" ht="23.1" customHeight="1">
+      <c r="A37" s="33" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="B37" s="43"/>
-      <c r="C37" s="12" t="str">
+      <c r="B37" s="34"/>
+      <c r="C37" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="D37" s="44"/>
-      <c r="E37" s="45"/>
-      <c r="F37" s="46"/>
-      <c r="G37" s="47"/>
-      <c r="H37" s="46"/>
-      <c r="I37" s="47"/>
-      <c r="J37" s="40" t="str">
+      <c r="D37" s="35"/>
+      <c r="E37" s="36"/>
+      <c r="F37" s="37"/>
+      <c r="G37" s="38"/>
+      <c r="H37" s="37"/>
+      <c r="I37" s="38"/>
+      <c r="J37" s="31" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K37" s="41"/>
-      <c r="L37" s="37"/>
-      <c r="M37" s="38"/>
-      <c r="N37" s="38"/>
-      <c r="O37" s="38"/>
-      <c r="P37" s="38"/>
-      <c r="Q37" s="38"/>
-      <c r="R37" s="38"/>
-      <c r="S37" s="38"/>
-      <c r="T37" s="38"/>
-      <c r="U37" s="38"/>
-      <c r="V37" s="39"/>
-      <c r="W37" s="14"/>
-      <c r="AB37" s="4"/>
-    </row>
-    <row r="38" spans="1:28" ht="23.1" customHeight="1">
-      <c r="A38" s="42" t="str">
+      <c r="K37" s="32"/>
+      <c r="L37" s="28"/>
+      <c r="M37" s="29"/>
+      <c r="N37" s="29"/>
+      <c r="O37" s="29"/>
+      <c r="P37" s="29"/>
+      <c r="Q37" s="29"/>
+      <c r="R37" s="29"/>
+      <c r="S37" s="29"/>
+      <c r="T37" s="29"/>
+      <c r="U37" s="29"/>
+      <c r="V37" s="30"/>
+    </row>
+    <row r="38" spans="1:22" ht="23.1" customHeight="1">
+      <c r="A38" s="33" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="B38" s="43"/>
-      <c r="C38" s="12" t="str">
+      <c r="B38" s="34"/>
+      <c r="C38" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="D38" s="46"/>
-      <c r="E38" s="47"/>
-      <c r="F38" s="46"/>
-      <c r="G38" s="47"/>
-      <c r="H38" s="46"/>
-      <c r="I38" s="47"/>
-      <c r="J38" s="40" t="str">
+      <c r="D38" s="37"/>
+      <c r="E38" s="38"/>
+      <c r="F38" s="37"/>
+      <c r="G38" s="38"/>
+      <c r="H38" s="37"/>
+      <c r="I38" s="38"/>
+      <c r="J38" s="31" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K38" s="41"/>
-      <c r="L38" s="37"/>
-      <c r="M38" s="38"/>
-      <c r="N38" s="38"/>
-      <c r="O38" s="38"/>
-      <c r="P38" s="38"/>
-      <c r="Q38" s="38"/>
-      <c r="R38" s="38"/>
-      <c r="S38" s="38"/>
-      <c r="T38" s="38"/>
-      <c r="U38" s="38"/>
-      <c r="V38" s="39"/>
-      <c r="W38" s="14"/>
-      <c r="AB38" s="4"/>
-    </row>
-    <row r="39" spans="1:28" ht="23.1" customHeight="1">
-      <c r="A39" s="42" t="str">
+      <c r="K38" s="32"/>
+      <c r="L38" s="28"/>
+      <c r="M38" s="29"/>
+      <c r="N38" s="29"/>
+      <c r="O38" s="29"/>
+      <c r="P38" s="29"/>
+      <c r="Q38" s="29"/>
+      <c r="R38" s="29"/>
+      <c r="S38" s="29"/>
+      <c r="T38" s="29"/>
+      <c r="U38" s="29"/>
+      <c r="V38" s="30"/>
+    </row>
+    <row r="39" spans="1:22" ht="23.1" customHeight="1">
+      <c r="A39" s="33" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="B39" s="43"/>
-      <c r="C39" s="12" t="str">
+      <c r="B39" s="34"/>
+      <c r="C39" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="D39" s="46"/>
-      <c r="E39" s="47"/>
-      <c r="F39" s="46"/>
-      <c r="G39" s="47"/>
-      <c r="H39" s="46"/>
-      <c r="I39" s="47"/>
-      <c r="J39" s="40" t="str">
+      <c r="D39" s="37"/>
+      <c r="E39" s="38"/>
+      <c r="F39" s="37"/>
+      <c r="G39" s="38"/>
+      <c r="H39" s="37"/>
+      <c r="I39" s="38"/>
+      <c r="J39" s="31" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K39" s="41"/>
-      <c r="L39" s="37"/>
-      <c r="M39" s="38"/>
-      <c r="N39" s="38"/>
-      <c r="O39" s="38"/>
-      <c r="P39" s="38"/>
-      <c r="Q39" s="38"/>
-      <c r="R39" s="38"/>
-      <c r="S39" s="38"/>
-      <c r="T39" s="38"/>
-      <c r="U39" s="38"/>
-      <c r="V39" s="39"/>
-      <c r="W39" s="14"/>
-      <c r="AB39" s="4"/>
-    </row>
-    <row r="40" spans="1:28" ht="23.1" customHeight="1">
-      <c r="A40" s="42" t="str">
+      <c r="K39" s="32"/>
+      <c r="L39" s="28"/>
+      <c r="M39" s="29"/>
+      <c r="N39" s="29"/>
+      <c r="O39" s="29"/>
+      <c r="P39" s="29"/>
+      <c r="Q39" s="29"/>
+      <c r="R39" s="29"/>
+      <c r="S39" s="29"/>
+      <c r="T39" s="29"/>
+      <c r="U39" s="29"/>
+      <c r="V39" s="30"/>
+    </row>
+    <row r="40" spans="1:22" ht="23.1" customHeight="1">
+      <c r="A40" s="33" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="B40" s="43"/>
-      <c r="C40" s="12" t="str">
+      <c r="B40" s="34"/>
+      <c r="C40" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="D40" s="44"/>
-      <c r="E40" s="45"/>
-      <c r="F40" s="46"/>
-      <c r="G40" s="47"/>
-      <c r="H40" s="46"/>
-      <c r="I40" s="47"/>
-      <c r="J40" s="40" t="str">
+      <c r="D40" s="35"/>
+      <c r="E40" s="36"/>
+      <c r="F40" s="37"/>
+      <c r="G40" s="38"/>
+      <c r="H40" s="37"/>
+      <c r="I40" s="38"/>
+      <c r="J40" s="31" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K40" s="41"/>
-      <c r="L40" s="37"/>
-      <c r="M40" s="38"/>
-      <c r="N40" s="38"/>
-      <c r="O40" s="38"/>
-      <c r="P40" s="38"/>
-      <c r="Q40" s="38"/>
-      <c r="R40" s="38"/>
-      <c r="S40" s="38"/>
-      <c r="T40" s="38"/>
-      <c r="U40" s="38"/>
-      <c r="V40" s="39"/>
-      <c r="W40" s="14"/>
-      <c r="AB40" s="4"/>
-    </row>
-    <row r="41" spans="1:28" ht="23.1" customHeight="1">
-      <c r="A41" s="42" t="str">
+      <c r="K40" s="32"/>
+      <c r="L40" s="28"/>
+      <c r="M40" s="29"/>
+      <c r="N40" s="29"/>
+      <c r="O40" s="29"/>
+      <c r="P40" s="29"/>
+      <c r="Q40" s="29"/>
+      <c r="R40" s="29"/>
+      <c r="S40" s="29"/>
+      <c r="T40" s="29"/>
+      <c r="U40" s="29"/>
+      <c r="V40" s="30"/>
+    </row>
+    <row r="41" spans="1:22" ht="23.1" customHeight="1">
+      <c r="A41" s="33" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="B41" s="43"/>
-      <c r="C41" s="12" t="str">
+      <c r="B41" s="34"/>
+      <c r="C41" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="D41" s="44"/>
-      <c r="E41" s="45"/>
-      <c r="F41" s="46"/>
-      <c r="G41" s="47"/>
-      <c r="H41" s="46"/>
-      <c r="I41" s="47"/>
-      <c r="J41" s="40" t="str">
+      <c r="D41" s="35"/>
+      <c r="E41" s="36"/>
+      <c r="F41" s="37"/>
+      <c r="G41" s="38"/>
+      <c r="H41" s="37"/>
+      <c r="I41" s="38"/>
+      <c r="J41" s="31" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K41" s="41"/>
-      <c r="L41" s="37"/>
-      <c r="M41" s="38"/>
-      <c r="N41" s="38"/>
-      <c r="O41" s="38"/>
-      <c r="P41" s="38"/>
-      <c r="Q41" s="38"/>
-      <c r="R41" s="38"/>
-      <c r="S41" s="38"/>
-      <c r="T41" s="38"/>
-      <c r="U41" s="38"/>
-      <c r="V41" s="39"/>
-      <c r="W41" s="14"/>
-      <c r="AB41" s="4"/>
-    </row>
-    <row r="42" spans="1:28" ht="23.1" customHeight="1">
-      <c r="A42" s="42" t="str">
+      <c r="K41" s="32"/>
+      <c r="L41" s="28"/>
+      <c r="M41" s="29"/>
+      <c r="N41" s="29"/>
+      <c r="O41" s="29"/>
+      <c r="P41" s="29"/>
+      <c r="Q41" s="29"/>
+      <c r="R41" s="29"/>
+      <c r="S41" s="29"/>
+      <c r="T41" s="29"/>
+      <c r="U41" s="29"/>
+      <c r="V41" s="30"/>
+    </row>
+    <row r="42" spans="1:22" ht="23.1" customHeight="1">
+      <c r="A42" s="33" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="B42" s="43"/>
-      <c r="C42" s="12" t="str">
+      <c r="B42" s="34"/>
+      <c r="C42" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="D42" s="44"/>
-      <c r="E42" s="45"/>
-      <c r="F42" s="46"/>
-      <c r="G42" s="47"/>
-      <c r="H42" s="46"/>
-      <c r="I42" s="47"/>
-      <c r="J42" s="40" t="str">
+      <c r="D42" s="35"/>
+      <c r="E42" s="36"/>
+      <c r="F42" s="37"/>
+      <c r="G42" s="38"/>
+      <c r="H42" s="37"/>
+      <c r="I42" s="38"/>
+      <c r="J42" s="31" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K42" s="41"/>
-      <c r="L42" s="37"/>
-      <c r="M42" s="38"/>
-      <c r="N42" s="38"/>
-      <c r="O42" s="38"/>
-      <c r="P42" s="38"/>
-      <c r="Q42" s="38"/>
-      <c r="R42" s="38"/>
-      <c r="S42" s="38"/>
-      <c r="T42" s="38"/>
-      <c r="U42" s="38"/>
-      <c r="V42" s="39"/>
-      <c r="W42" s="14"/>
-      <c r="AB42" s="4"/>
-    </row>
-    <row r="43" spans="1:28" ht="23.1" customHeight="1">
-      <c r="A43" s="42" t="str">
+      <c r="K42" s="32"/>
+      <c r="L42" s="28"/>
+      <c r="M42" s="29"/>
+      <c r="N42" s="29"/>
+      <c r="O42" s="29"/>
+      <c r="P42" s="29"/>
+      <c r="Q42" s="29"/>
+      <c r="R42" s="29"/>
+      <c r="S42" s="29"/>
+      <c r="T42" s="29"/>
+      <c r="U42" s="29"/>
+      <c r="V42" s="30"/>
+    </row>
+    <row r="43" spans="1:22" ht="23.1" customHeight="1">
+      <c r="A43" s="33" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="B43" s="43"/>
-      <c r="C43" s="12" t="str">
+      <c r="B43" s="34"/>
+      <c r="C43" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="D43" s="44"/>
-      <c r="E43" s="45"/>
-      <c r="F43" s="46"/>
-      <c r="G43" s="47"/>
-      <c r="H43" s="46"/>
-      <c r="I43" s="47"/>
-      <c r="J43" s="40" t="str">
+      <c r="D43" s="35"/>
+      <c r="E43" s="36"/>
+      <c r="F43" s="37"/>
+      <c r="G43" s="38"/>
+      <c r="H43" s="37"/>
+      <c r="I43" s="38"/>
+      <c r="J43" s="31" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K43" s="41"/>
-      <c r="L43" s="37"/>
-      <c r="M43" s="38"/>
-      <c r="N43" s="38"/>
-      <c r="O43" s="38"/>
-      <c r="P43" s="38"/>
-      <c r="Q43" s="38"/>
-      <c r="R43" s="38"/>
-      <c r="S43" s="38"/>
-      <c r="T43" s="38"/>
-      <c r="U43" s="38"/>
-      <c r="V43" s="39"/>
-      <c r="W43" s="14"/>
-      <c r="AB43" s="4"/>
-    </row>
-    <row r="44" spans="1:28" ht="23.1" customHeight="1">
-      <c r="A44" s="42" t="str">
+      <c r="K43" s="32"/>
+      <c r="L43" s="28"/>
+      <c r="M43" s="29"/>
+      <c r="N43" s="29"/>
+      <c r="O43" s="29"/>
+      <c r="P43" s="29"/>
+      <c r="Q43" s="29"/>
+      <c r="R43" s="29"/>
+      <c r="S43" s="29"/>
+      <c r="T43" s="29"/>
+      <c r="U43" s="29"/>
+      <c r="V43" s="30"/>
+    </row>
+    <row r="44" spans="1:22" ht="23.1" customHeight="1">
+      <c r="A44" s="33" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="B44" s="43"/>
-      <c r="C44" s="12" t="str">
+      <c r="B44" s="34"/>
+      <c r="C44" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="D44" s="46"/>
-      <c r="E44" s="47"/>
-      <c r="F44" s="46"/>
-      <c r="G44" s="47"/>
-      <c r="H44" s="46"/>
-      <c r="I44" s="47"/>
-      <c r="J44" s="40" t="str">
+      <c r="D44" s="37"/>
+      <c r="E44" s="38"/>
+      <c r="F44" s="37"/>
+      <c r="G44" s="38"/>
+      <c r="H44" s="37"/>
+      <c r="I44" s="38"/>
+      <c r="J44" s="31" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K44" s="41"/>
-      <c r="L44" s="37"/>
-      <c r="M44" s="38"/>
-      <c r="N44" s="38"/>
-      <c r="O44" s="38"/>
-      <c r="P44" s="38"/>
-      <c r="Q44" s="38"/>
-      <c r="R44" s="38"/>
-      <c r="S44" s="38"/>
-      <c r="T44" s="38"/>
-      <c r="U44" s="38"/>
-      <c r="V44" s="39"/>
-      <c r="W44" s="14"/>
-      <c r="AB44" s="4"/>
-    </row>
-    <row r="45" spans="1:28" ht="23.1" customHeight="1">
-      <c r="A45" s="13"/>
-      <c r="B45" s="13"/>
-      <c r="C45" s="13"/>
-      <c r="D45" s="13"/>
-      <c r="E45" s="13"/>
-      <c r="F45" s="13"/>
-      <c r="G45" s="13"/>
-      <c r="H45" s="13"/>
-      <c r="I45" s="13"/>
-      <c r="J45" s="13"/>
-      <c r="K45" s="13"/>
-      <c r="L45" s="13"/>
-      <c r="M45" s="13"/>
-      <c r="N45" s="13"/>
-      <c r="O45" s="13"/>
-      <c r="P45" s="13"/>
-      <c r="Q45" s="13"/>
-      <c r="R45" s="13"/>
-      <c r="S45" s="13"/>
-      <c r="T45" s="13"/>
-      <c r="U45" s="13"/>
-      <c r="V45" s="13"/>
-      <c r="W45" s="13"/>
-      <c r="X45" s="13"/>
-      <c r="Y45" s="13"/>
-      <c r="Z45" s="13"/>
-      <c r="AA45" s="10"/>
-    </row>
-    <row r="46" spans="1:28" ht="23.1" customHeight="1">
-      <c r="A46" s="34" t="s">
+      <c r="K44" s="32"/>
+      <c r="L44" s="28"/>
+      <c r="M44" s="29"/>
+      <c r="N44" s="29"/>
+      <c r="O44" s="29"/>
+      <c r="P44" s="29"/>
+      <c r="Q44" s="29"/>
+      <c r="R44" s="29"/>
+      <c r="S44" s="29"/>
+      <c r="T44" s="29"/>
+      <c r="U44" s="29"/>
+      <c r="V44" s="30"/>
+    </row>
+    <row r="45" spans="1:22" ht="23.1" customHeight="1">
+      <c r="A45" s="10"/>
+      <c r="B45" s="10"/>
+      <c r="C45" s="10"/>
+      <c r="D45" s="10"/>
+      <c r="E45" s="10"/>
+      <c r="F45" s="10"/>
+      <c r="G45" s="10"/>
+      <c r="H45" s="10"/>
+      <c r="I45" s="10"/>
+      <c r="J45" s="10"/>
+      <c r="K45" s="10"/>
+      <c r="L45" s="10"/>
+      <c r="M45" s="10"/>
+      <c r="N45" s="10"/>
+      <c r="O45" s="10"/>
+      <c r="P45" s="10"/>
+      <c r="Q45" s="10"/>
+      <c r="R45" s="10"/>
+      <c r="S45" s="10"/>
+      <c r="T45" s="10"/>
+      <c r="U45" s="10"/>
+      <c r="V45" s="10"/>
+    </row>
+    <row r="46" spans="1:22" ht="23.1" customHeight="1">
+      <c r="A46" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="B46" s="35"/>
-      <c r="C46" s="35"/>
-      <c r="D46" s="35"/>
-      <c r="E46" s="35"/>
-      <c r="F46" s="35"/>
-      <c r="G46" s="35"/>
-      <c r="H46" s="35"/>
-      <c r="I46" s="35"/>
-      <c r="J46" s="35"/>
-      <c r="K46" s="35"/>
-      <c r="L46" s="35"/>
-      <c r="M46" s="35"/>
-      <c r="N46" s="35"/>
-      <c r="O46" s="35"/>
-      <c r="P46" s="35"/>
-      <c r="Q46" s="35"/>
-      <c r="R46" s="35"/>
-      <c r="S46" s="35"/>
-      <c r="T46" s="35"/>
-      <c r="U46" s="35"/>
-      <c r="V46" s="36"/>
-      <c r="W46" s="13"/>
-      <c r="X46" s="13"/>
-      <c r="Y46" s="13"/>
-      <c r="Z46" s="13"/>
-      <c r="AA46" s="10"/>
-    </row>
-    <row r="47" spans="1:28" ht="23.1" customHeight="1">
-      <c r="A47" s="28"/>
-      <c r="B47" s="29"/>
-      <c r="C47" s="29"/>
-      <c r="D47" s="29"/>
-      <c r="E47" s="29"/>
-      <c r="F47" s="29"/>
-      <c r="G47" s="29"/>
-      <c r="H47" s="29"/>
-      <c r="I47" s="29"/>
-      <c r="J47" s="29"/>
-      <c r="K47" s="29"/>
-      <c r="L47" s="29"/>
-      <c r="M47" s="29"/>
-      <c r="N47" s="29"/>
-      <c r="O47" s="29"/>
-      <c r="P47" s="29"/>
-      <c r="Q47" s="29"/>
-      <c r="R47" s="29"/>
-      <c r="S47" s="29"/>
-      <c r="T47" s="29"/>
-      <c r="U47" s="29"/>
-      <c r="V47" s="30"/>
-      <c r="W47" s="25"/>
-      <c r="X47" s="25"/>
-      <c r="Y47" s="25"/>
-      <c r="Z47" s="13"/>
-      <c r="AA47" s="10"/>
-    </row>
-    <row r="48" spans="1:28" ht="23.1" customHeight="1">
-      <c r="A48" s="28"/>
-      <c r="B48" s="29"/>
-      <c r="C48" s="29"/>
-      <c r="D48" s="29"/>
-      <c r="E48" s="29"/>
-      <c r="F48" s="29"/>
-      <c r="G48" s="29"/>
-      <c r="H48" s="29"/>
-      <c r="I48" s="29"/>
-      <c r="J48" s="29"/>
-      <c r="K48" s="29"/>
-      <c r="L48" s="29"/>
-      <c r="M48" s="29"/>
-      <c r="N48" s="29"/>
-      <c r="O48" s="29"/>
-      <c r="P48" s="29"/>
-      <c r="Q48" s="29"/>
-      <c r="R48" s="29"/>
-      <c r="S48" s="29"/>
-      <c r="T48" s="29"/>
-      <c r="U48" s="29"/>
-      <c r="V48" s="30"/>
-      <c r="W48" s="25"/>
-      <c r="X48" s="25"/>
-      <c r="Y48" s="25"/>
-      <c r="Z48" s="13"/>
-      <c r="AA48" s="10"/>
-    </row>
-    <row r="49" spans="1:27" ht="23.1" customHeight="1">
-      <c r="A49" s="31"/>
-      <c r="B49" s="32"/>
-      <c r="C49" s="32"/>
-      <c r="D49" s="32"/>
-      <c r="E49" s="32"/>
-      <c r="F49" s="32"/>
-      <c r="G49" s="32"/>
-      <c r="H49" s="32"/>
-      <c r="I49" s="32"/>
-      <c r="J49" s="32"/>
-      <c r="K49" s="32"/>
-      <c r="L49" s="32"/>
-      <c r="M49" s="32"/>
-      <c r="N49" s="32"/>
-      <c r="O49" s="32"/>
-      <c r="P49" s="32"/>
-      <c r="Q49" s="32"/>
-      <c r="R49" s="32"/>
-      <c r="S49" s="32"/>
-      <c r="T49" s="32"/>
-      <c r="U49" s="32"/>
-      <c r="V49" s="33"/>
-      <c r="W49" s="25"/>
-      <c r="X49" s="25"/>
-      <c r="Y49" s="25"/>
-      <c r="Z49" s="13"/>
-      <c r="AA49" s="10"/>
+      <c r="B46" s="26"/>
+      <c r="C46" s="26"/>
+      <c r="D46" s="26"/>
+      <c r="E46" s="26"/>
+      <c r="F46" s="26"/>
+      <c r="G46" s="26"/>
+      <c r="H46" s="26"/>
+      <c r="I46" s="26"/>
+      <c r="J46" s="26"/>
+      <c r="K46" s="26"/>
+      <c r="L46" s="26"/>
+      <c r="M46" s="26"/>
+      <c r="N46" s="26"/>
+      <c r="O46" s="26"/>
+      <c r="P46" s="26"/>
+      <c r="Q46" s="26"/>
+      <c r="R46" s="26"/>
+      <c r="S46" s="26"/>
+      <c r="T46" s="26"/>
+      <c r="U46" s="26"/>
+      <c r="V46" s="27"/>
+    </row>
+    <row r="47" spans="1:22" ht="23.1" customHeight="1">
+      <c r="A47" s="19"/>
+      <c r="B47" s="20"/>
+      <c r="C47" s="20"/>
+      <c r="D47" s="20"/>
+      <c r="E47" s="20"/>
+      <c r="F47" s="20"/>
+      <c r="G47" s="20"/>
+      <c r="H47" s="20"/>
+      <c r="I47" s="20"/>
+      <c r="J47" s="20"/>
+      <c r="K47" s="20"/>
+      <c r="L47" s="20"/>
+      <c r="M47" s="20"/>
+      <c r="N47" s="20"/>
+      <c r="O47" s="20"/>
+      <c r="P47" s="20"/>
+      <c r="Q47" s="20"/>
+      <c r="R47" s="20"/>
+      <c r="S47" s="20"/>
+      <c r="T47" s="20"/>
+      <c r="U47" s="20"/>
+      <c r="V47" s="21"/>
+    </row>
+    <row r="48" spans="1:22" ht="23.1" customHeight="1">
+      <c r="A48" s="19"/>
+      <c r="B48" s="20"/>
+      <c r="C48" s="20"/>
+      <c r="D48" s="20"/>
+      <c r="E48" s="20"/>
+      <c r="F48" s="20"/>
+      <c r="G48" s="20"/>
+      <c r="H48" s="20"/>
+      <c r="I48" s="20"/>
+      <c r="J48" s="20"/>
+      <c r="K48" s="20"/>
+      <c r="L48" s="20"/>
+      <c r="M48" s="20"/>
+      <c r="N48" s="20"/>
+      <c r="O48" s="20"/>
+      <c r="P48" s="20"/>
+      <c r="Q48" s="20"/>
+      <c r="R48" s="20"/>
+      <c r="S48" s="20"/>
+      <c r="T48" s="20"/>
+      <c r="U48" s="20"/>
+      <c r="V48" s="21"/>
+    </row>
+    <row r="49" spans="1:22" ht="23.1" customHeight="1">
+      <c r="A49" s="22"/>
+      <c r="B49" s="23"/>
+      <c r="C49" s="23"/>
+      <c r="D49" s="23"/>
+      <c r="E49" s="23"/>
+      <c r="F49" s="23"/>
+      <c r="G49" s="23"/>
+      <c r="H49" s="23"/>
+      <c r="I49" s="23"/>
+      <c r="J49" s="23"/>
+      <c r="K49" s="23"/>
+      <c r="L49" s="23"/>
+      <c r="M49" s="23"/>
+      <c r="N49" s="23"/>
+      <c r="O49" s="23"/>
+      <c r="P49" s="23"/>
+      <c r="Q49" s="23"/>
+      <c r="R49" s="23"/>
+      <c r="S49" s="23"/>
+      <c r="T49" s="23"/>
+      <c r="U49" s="23"/>
+      <c r="V49" s="24"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
-  <mergeCells count="225">
+  <mergeCells count="219">
     <mergeCell ref="H27:I27"/>
     <mergeCell ref="J27:K27"/>
     <mergeCell ref="H26:I26"/>
@@ -3195,13 +2997,10 @@
     <mergeCell ref="H19:I19"/>
     <mergeCell ref="H18:I18"/>
     <mergeCell ref="H17:I17"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="D13:E13"/>
     <mergeCell ref="F13:G13"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="D14:E14"/>
     <mergeCell ref="F14:G14"/>
-    <mergeCell ref="L7:M7"/>
     <mergeCell ref="H13:I13"/>
     <mergeCell ref="J13:K13"/>
     <mergeCell ref="A7:D7"/>
@@ -3209,10 +3008,6 @@
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="J15:K15"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="X5:Y7"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="L6:M6"/>
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="E6:G6"/>
     <mergeCell ref="H14:I14"/>
@@ -3223,13 +3018,14 @@
     <mergeCell ref="F11:G12"/>
     <mergeCell ref="H11:I12"/>
     <mergeCell ref="J11:K12"/>
-    <mergeCell ref="I6:K6"/>
     <mergeCell ref="L11:V12"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="E8:G8"/>
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="E9:G9"/>
     <mergeCell ref="A11:C12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="D13:E13"/>
     <mergeCell ref="A1:J2"/>
     <mergeCell ref="Q1:R2"/>
     <mergeCell ref="A4:D4"/>
@@ -3396,7 +3192,7 @@
       <formula>#REF!="振替稼働"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S1 W1:Y2">
+  <conditionalFormatting sqref="S1">
     <cfRule type="containsText" dxfId="0" priority="9" operator="containsText" text="入力してください">
       <formula>NOT(ISERROR(SEARCH("入力してください",S1)))</formula>
     </cfRule>
@@ -3405,7 +3201,7 @@
     <dataValidation type="decimal" imeMode="off" operator="greaterThanOrEqual" allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" error="半角で時刻を入力してください　例)10:00" sqref="E4:G6 D13:K44" xr:uid="{47CC238B-533E-4FBF-891A-2E863C4F6A4B}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation imeMode="hiragana" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L14:V44 S1 W1:Y2 W47:Y49 A47" xr:uid="{52D4DF7A-1DCB-45EB-9020-1B299194C4C6}"/>
+    <dataValidation imeMode="hiragana" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L14:V44 S1 A47" xr:uid="{52D4DF7A-1DCB-45EB-9020-1B299194C4C6}"/>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0" footer="0"/>
